--- a/artfynd/A 18885-2024 artfynd.xlsx
+++ b/artfynd/A 18885-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY61"/>
+  <dimension ref="A1:AY60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6513,10 +6513,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>103381193</v>
+        <v>103381202</v>
       </c>
       <c r="B54" t="n">
-        <v>95511</v>
+        <v>96251</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6529,21 +6529,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221944</v>
+        <v>219790</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lopplummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6553,10 +6553,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>367723.3720154802</v>
+        <v>367816.4265008466</v>
       </c>
       <c r="R54" t="n">
-        <v>6952354.470218086</v>
+        <v>6951929.960814255</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6625,7 +6625,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>103381202</v>
+        <v>103381174</v>
       </c>
       <c r="B55" t="n">
         <v>96251</v>
@@ -6665,10 +6665,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>367816.4265008466</v>
+        <v>367393.5962226755</v>
       </c>
       <c r="R55" t="n">
-        <v>6951929.960814255</v>
+        <v>6949462.528218168</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6737,10 +6737,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>103381174</v>
+        <v>103381144</v>
       </c>
       <c r="B56" t="n">
-        <v>96251</v>
+        <v>96354</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6753,21 +6753,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6777,10 +6777,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>367393.5962226755</v>
+        <v>367808.0784249112</v>
       </c>
       <c r="R56" t="n">
-        <v>6949462.528218168</v>
+        <v>6950352.469164949</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6849,10 +6849,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>103381144</v>
+        <v>103381168</v>
       </c>
       <c r="B57" t="n">
-        <v>96354</v>
+        <v>96251</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6865,21 +6865,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6889,10 +6889,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>367808.0784249112</v>
+        <v>367443.4093116862</v>
       </c>
       <c r="R57" t="n">
-        <v>6950352.469164949</v>
+        <v>6949784.985699547</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6961,7 +6961,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>103381168</v>
+        <v>103381206</v>
       </c>
       <c r="B58" t="n">
         <v>96251</v>
@@ -7001,10 +7001,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>367443.4093116862</v>
+        <v>367847.7863871052</v>
       </c>
       <c r="R58" t="n">
-        <v>6949784.985699547</v>
+        <v>6951885.01428475</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7073,7 +7073,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>103381206</v>
+        <v>103381163</v>
       </c>
       <c r="B59" t="n">
         <v>96251</v>
@@ -7113,10 +7113,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>367847.7863871052</v>
+        <v>367461.5807364698</v>
       </c>
       <c r="R59" t="n">
-        <v>6951885.01428475</v>
+        <v>6949870.312718078</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7185,10 +7185,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>103381163</v>
+        <v>103381201</v>
       </c>
       <c r="B60" t="n">
-        <v>96251</v>
+        <v>96336</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7201,21 +7201,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>219790</v>
+        <v>219811</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>367461.5807364698</v>
+        <v>367803.7356686802</v>
       </c>
       <c r="R60" t="n">
-        <v>6949870.312718078</v>
+        <v>6951969.560286601</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7294,118 +7294,6 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>103381201</v>
-      </c>
-      <c r="B61" t="n">
-        <v>96336</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
-        <v>219811</v>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Brudsporre</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Gymnadenia conopsea</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>Bruksvallarna, Hjd</t>
-        </is>
-      </c>
-      <c r="Q61" t="n">
-        <v>367803.7356686802</v>
-      </c>
-      <c r="R61" t="n">
-        <v>6951969.560286601</v>
-      </c>
-      <c r="S61" t="n">
-        <v>10</v>
-      </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W61" t="inlineStr">
-        <is>
-          <t>Tännäs</t>
-        </is>
-      </c>
-      <c r="Y61" t="inlineStr">
-        <is>
-          <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA61" t="inlineStr">
-        <is>
-          <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT61" t="inlineStr"/>
-      <c r="AW61" t="inlineStr">
-        <is>
-          <t>Brita Danielsson</t>
-        </is>
-      </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>Brita Danielsson, Anna Dahlin</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18885-2024 artfynd.xlsx
+++ b/artfynd/A 18885-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY60"/>
+  <dimension ref="A1:AY61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6513,10 +6513,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>103381202</v>
+        <v>103381193</v>
       </c>
       <c r="B54" t="n">
-        <v>96251</v>
+        <v>95511</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6529,21 +6529,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>219790</v>
+        <v>221944</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lopplummer</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Huperzia selago</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6553,10 +6553,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>367816.4265008466</v>
+        <v>367723.3720154802</v>
       </c>
       <c r="R54" t="n">
-        <v>6951929.960814255</v>
+        <v>6952354.470218086</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6625,7 +6625,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>103381174</v>
+        <v>103381202</v>
       </c>
       <c r="B55" t="n">
         <v>96251</v>
@@ -6665,10 +6665,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>367393.5962226755</v>
+        <v>367816.4265008466</v>
       </c>
       <c r="R55" t="n">
-        <v>6949462.528218168</v>
+        <v>6951929.960814255</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6737,10 +6737,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>103381144</v>
+        <v>103381174</v>
       </c>
       <c r="B56" t="n">
-        <v>96354</v>
+        <v>96251</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6753,21 +6753,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6777,10 +6777,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>367808.0784249112</v>
+        <v>367393.5962226755</v>
       </c>
       <c r="R56" t="n">
-        <v>6950352.469164949</v>
+        <v>6949462.528218168</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6849,10 +6849,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>103381168</v>
+        <v>103381144</v>
       </c>
       <c r="B57" t="n">
-        <v>96251</v>
+        <v>96354</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6865,21 +6865,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6889,10 +6889,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>367443.4093116862</v>
+        <v>367808.0784249112</v>
       </c>
       <c r="R57" t="n">
-        <v>6949784.985699547</v>
+        <v>6950352.469164949</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6961,7 +6961,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>103381206</v>
+        <v>103381168</v>
       </c>
       <c r="B58" t="n">
         <v>96251</v>
@@ -7001,10 +7001,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>367847.7863871052</v>
+        <v>367443.4093116862</v>
       </c>
       <c r="R58" t="n">
-        <v>6951885.01428475</v>
+        <v>6949784.985699547</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7073,7 +7073,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>103381163</v>
+        <v>103381206</v>
       </c>
       <c r="B59" t="n">
         <v>96251</v>
@@ -7113,10 +7113,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>367461.5807364698</v>
+        <v>367847.7863871052</v>
       </c>
       <c r="R59" t="n">
-        <v>6949870.312718078</v>
+        <v>6951885.01428475</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7185,10 +7185,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>103381201</v>
+        <v>103381163</v>
       </c>
       <c r="B60" t="n">
-        <v>96336</v>
+        <v>96251</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7201,21 +7201,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>219811</v>
+        <v>219790</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>367803.7356686802</v>
+        <v>367461.5807364698</v>
       </c>
       <c r="R60" t="n">
-        <v>6951969.560286601</v>
+        <v>6949870.312718078</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7294,6 +7294,118 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>103381201</v>
+      </c>
+      <c r="B61" t="n">
+        <v>96336</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Bruksvallarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>367803.7356686802</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6951969.560286601</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Brita Danielsson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Brita Danielsson, Anna Dahlin</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18885-2024 artfynd.xlsx
+++ b/artfynd/A 18885-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY61"/>
+  <dimension ref="A1:AY104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,55 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>95024742</v>
+        <v>103381254</v>
       </c>
       <c r="B2" t="n">
-        <v>96242</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57369</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219788</v>
+        <v>102961</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lillåsen, Härjedalen, Hjd</t>
+          <t>Bruksvallarna, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>367559.3372999525</v>
+        <v>366675</v>
       </c>
       <c r="R2" t="n">
-        <v>6952650.278122743</v>
+        <v>6954702</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-07-22</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-07-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,27 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Brita Danielsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Brita Danielsson, Anna Dahlin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>95025423</v>
+        <v>103381231</v>
       </c>
       <c r="B3" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -823,21 +801,19 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bastukroken, Härjedalen, Hjd</t>
+          <t>Bruksvallarna, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>367465.8022504605</v>
+        <v>366951</v>
       </c>
       <c r="R3" t="n">
-        <v>6952877.950464357</v>
+        <v>6954125</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-07-22</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-07-22</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,27 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Brita Danielsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Brita Danielsson, Anna Dahlin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>95025210</v>
+        <v>103381260</v>
       </c>
       <c r="B4" t="n">
-        <v>96237</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,39 +880,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220093</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bastukroken, Härjedalen, Hjd</t>
+          <t>Bruksvallarna, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>367474.5639212863</v>
+        <v>366622</v>
       </c>
       <c r="R4" t="n">
-        <v>6952798.057061887</v>
+        <v>6954790</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -975,22 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-07-22</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-07-22</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,27 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Brita Danielsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Brita Danielsson, Anna Dahlin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>95025201</v>
+        <v>103381261</v>
       </c>
       <c r="B5" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,21 +995,19 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bastukroken, Härjedalen, Hjd</t>
+          <t>Bruksvallarna, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>367474.5639212863</v>
+        <v>366610</v>
       </c>
       <c r="R5" t="n">
-        <v>6952798.057061887</v>
+        <v>6954812</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1089,22 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-07-22</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-07-22</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,27 +1051,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Brita Danielsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Brita Danielsson, Anna Dahlin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>95025274</v>
+        <v>103381262</v>
       </c>
       <c r="B6" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,21 +1092,19 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lillåsen 200, Härjedalen, Hjd</t>
+          <t>Bruksvallarna, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>367454.523216757</v>
+        <v>366616</v>
       </c>
       <c r="R6" t="n">
-        <v>6952814.954518329</v>
+        <v>6954818</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,22 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-07-22</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-07-22</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,27 +1148,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Brita Danielsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Brita Danielsson, Anna Dahlin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>98105810</v>
+        <v>103381263</v>
       </c>
       <c r="B7" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1281,17 +1191,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lillåsvallen 2, Hjd</t>
+          <t>Bruksvallarna, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>367495.5021106853</v>
+        <v>366609</v>
       </c>
       <c r="R7" t="n">
-        <v>6952746.179800792</v>
+        <v>6954833</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1315,22 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-07-05</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-07-05</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,31 +1245,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Per Toräng</t>
+          <t>Brita Danielsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Per Toräng</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Adb inventering slåtterängar 2020-2021</t>
-        </is>
-      </c>
+          <t>Brita Danielsson, Anna Dahlin</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103381169</v>
+        <v>103381264</v>
       </c>
       <c r="B8" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1401,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>367435.4389563501</v>
+        <v>366605</v>
       </c>
       <c r="R8" t="n">
-        <v>6949770.118952043</v>
+        <v>6954836</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1434,19 +1325,9 @@
           <t>2021-07-13</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1473,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>103381155</v>
+        <v>103381266</v>
       </c>
       <c r="B9" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99017</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219790</v>
+        <v>219795</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1513,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>367514.5009694996</v>
+        <v>366608</v>
       </c>
       <c r="R9" t="n">
-        <v>6950017.74707697</v>
+        <v>6954851</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1546,19 +1422,9 @@
           <t>2021-07-13</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>103381160</v>
+        <v>103381227</v>
       </c>
       <c r="B10" t="n">
-        <v>96356</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99120</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219847</v>
+        <v>219811</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1625,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>367482.9320218301</v>
+        <v>366960</v>
       </c>
       <c r="R10" t="n">
-        <v>6949908.57170581</v>
+        <v>6954102</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1658,19 +1519,9 @@
           <t>2021-07-13</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1697,15 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>103381137</v>
+        <v>103381232</v>
       </c>
       <c r="B11" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99120</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1713,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221952</v>
+        <v>219811</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1737,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>367474.8154233048</v>
+        <v>366948</v>
       </c>
       <c r="R11" t="n">
-        <v>6949901.534454063</v>
+        <v>6954120</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1770,19 +1616,9 @@
           <t>2021-07-13</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1809,15 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>103381239</v>
+        <v>103381249</v>
       </c>
       <c r="B12" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99120</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219790</v>
+        <v>219811</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1849,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>367233.46993773</v>
+        <v>366847</v>
       </c>
       <c r="R12" t="n">
-        <v>6953225.668271866</v>
+        <v>6954498</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1882,19 +1713,9 @@
           <t>2021-07-13</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1921,15 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>103381164</v>
+        <v>103381241</v>
       </c>
       <c r="B13" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1937,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1961,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>367468.4638205143</v>
+        <v>366936</v>
       </c>
       <c r="R13" t="n">
-        <v>6949869.576325118</v>
+        <v>6954375</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1994,19 +1810,9 @@
           <t>2021-07-13</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2036,12 +1842,7 @@
         <v>103381196</v>
       </c>
       <c r="B14" t="n">
-        <v>57577</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58817</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2073,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>367667.6195958087</v>
+        <v>367667</v>
       </c>
       <c r="R14" t="n">
-        <v>6952491.436425587</v>
+        <v>6952492</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2106,19 +1907,9 @@
           <t>2021-07-13</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2145,15 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>103381151</v>
+        <v>95024742</v>
       </c>
       <c r="B15" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99026</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2161,16 +1947,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219790</v>
+        <v>219788</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2179,19 +1965,21 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bruksvallarna, Hjd</t>
+          <t>Lillåsen, Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>367685.6713442696</v>
+        <v>367560</v>
       </c>
       <c r="R15" t="n">
-        <v>6950229.91656538</v>
+        <v>6952650</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2215,22 +2003,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2245,27 +2023,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Brita Danielsson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Brita Danielsson, Anna Dahlin</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>103381205</v>
+        <v>95025201</v>
       </c>
       <c r="B16" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2291,19 +2064,21 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bruksvallarna, Hjd</t>
+          <t>Bastukroken, Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>367831.8948644529</v>
+        <v>367475</v>
       </c>
       <c r="R16" t="n">
-        <v>6951902.20718344</v>
+        <v>6952798</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2327,22 +2102,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-22</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2357,27 +2122,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Brita Danielsson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Brita Danielsson, Anna Dahlin</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>103381177</v>
+        <v>95025274</v>
       </c>
       <c r="B17" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2403,19 +2163,21 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bruksvallarna, Hjd</t>
+          <t>Lillåsen 200, Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>367396.5707072997</v>
+        <v>367455</v>
       </c>
       <c r="R17" t="n">
-        <v>6949375.881598422</v>
+        <v>6952815</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2439,22 +2201,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-22</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2469,27 +2221,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Brita Danielsson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Brita Danielsson, Anna Dahlin</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>103381162</v>
+        <v>95025423</v>
       </c>
       <c r="B18" t="n">
-        <v>96336</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2497,37 +2244,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219811</v>
+        <v>219790</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bruksvallarna, Hjd</t>
+          <t>Bastukroken, Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>367465.8523408996</v>
+        <v>367465</v>
       </c>
       <c r="R18" t="n">
-        <v>6949896.371909354</v>
+        <v>6952878</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2551,22 +2300,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-22</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-22</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2581,27 +2320,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Brita Danielsson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Brita Danielsson, Anna Dahlin</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>103381214</v>
+        <v>98105810</v>
       </c>
       <c r="B19" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2609,37 +2343,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bruksvallarna, Hjd</t>
+          <t>Lillåsvallen 2, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>367938.5412522755</v>
+        <v>367495</v>
       </c>
       <c r="R19" t="n">
-        <v>6951367.629462905</v>
+        <v>6952746</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2663,22 +2397,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-05</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2693,27 +2417,26 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Brita Danielsson</t>
+          <t>Per Toräng</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Brita Danielsson, Anna Dahlin</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
+          <t>Per Toräng</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Adb inventering slåtterängar 2020-2021</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>103381224</v>
+        <v>103381146</v>
       </c>
       <c r="B20" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2721,21 +2444,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2745,10 +2468,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>367242.6441479025</v>
+        <v>367783</v>
       </c>
       <c r="R20" t="n">
-        <v>6953224.839296329</v>
+        <v>6950288</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2778,19 +2501,9 @@
           <t>2021-07-13</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2817,15 +2530,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>103381165</v>
+        <v>103381147</v>
       </c>
       <c r="B21" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2833,21 +2541,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2857,10 +2565,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>367471.5186078844</v>
+        <v>367755</v>
       </c>
       <c r="R21" t="n">
-        <v>6949865.312053433</v>
+        <v>6950289</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2890,19 +2598,9 @@
           <t>2021-07-13</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2929,15 +2627,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>103381143</v>
+        <v>103381148</v>
       </c>
       <c r="B22" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2945,21 +2638,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2969,10 +2662,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>367540.2113820165</v>
+        <v>367678</v>
       </c>
       <c r="R22" t="n">
-        <v>6950038.343555203</v>
+        <v>6950246</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3002,19 +2695,9 @@
           <t>2021-07-13</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3041,15 +2724,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>103381146</v>
+        <v>103381150</v>
       </c>
       <c r="B23" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3081,10 +2759,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>367782.924966295</v>
+        <v>367690</v>
       </c>
       <c r="R23" t="n">
-        <v>6950288.138945187</v>
+        <v>6950242</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3114,19 +2792,9 @@
           <t>2021-07-13</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3153,15 +2821,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>103381156</v>
+        <v>103381151</v>
       </c>
       <c r="B24" t="n">
-        <v>96252</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3169,21 +2832,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>223591</v>
+        <v>219790</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3193,10 +2856,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>367514.9406176917</v>
+        <v>367686</v>
       </c>
       <c r="R24" t="n">
-        <v>6949982.75657879</v>
+        <v>6950230</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3226,19 +2889,9 @@
           <t>2021-07-13</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3265,15 +2918,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>103381142</v>
+        <v>103381153</v>
       </c>
       <c r="B25" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3281,21 +2929,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3305,10 +2953,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>367524.5306022654</v>
+        <v>367898</v>
       </c>
       <c r="R25" t="n">
-        <v>6950015.043915023</v>
+        <v>6950694</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3338,19 +2986,9 @@
           <t>2021-07-13</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3377,15 +3015,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>103381179</v>
+        <v>103381155</v>
       </c>
       <c r="B26" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3417,10 +3050,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>367918.948140459</v>
+        <v>367515</v>
       </c>
       <c r="R26" t="n">
-        <v>6951004.553431124</v>
+        <v>6950018</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3450,19 +3083,9 @@
           <t>2021-07-13</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3489,15 +3112,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>103381141</v>
+        <v>103381161</v>
       </c>
       <c r="B27" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3505,21 +3123,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3529,10 +3147,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>367524.604317114</v>
+        <v>367457</v>
       </c>
       <c r="R27" t="n">
-        <v>6950016.881625885</v>
+        <v>6949900</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3562,19 +3180,9 @@
           <t>2021-07-13</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3601,15 +3209,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>103381172</v>
+        <v>103381163</v>
       </c>
       <c r="B28" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3641,10 +3244,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>367432.8608535859</v>
+        <v>367461</v>
       </c>
       <c r="R28" t="n">
-        <v>6949751.814291549</v>
+        <v>6949871</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3674,19 +3277,9 @@
           <t>2021-07-13</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3713,15 +3306,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>103381216</v>
+        <v>103381164</v>
       </c>
       <c r="B29" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3753,10 +3341,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>367921.4844759196</v>
+        <v>367468</v>
       </c>
       <c r="R29" t="n">
-        <v>6951056.434390208</v>
+        <v>6949869</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3786,19 +3374,9 @@
           <t>2021-07-13</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3825,15 +3403,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>103381249</v>
+        <v>103381166</v>
       </c>
       <c r="B30" t="n">
-        <v>96336</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3841,21 +3414,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219811</v>
+        <v>219790</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3865,10 +3438,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>366846.5481672774</v>
+        <v>367449</v>
       </c>
       <c r="R30" t="n">
-        <v>6954497.466646577</v>
+        <v>6949852</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3898,19 +3471,9 @@
           <t>2021-07-13</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3937,15 +3500,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>103381244</v>
+        <v>103381167</v>
       </c>
       <c r="B31" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3977,10 +3535,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>367436.6238312022</v>
+        <v>367445</v>
       </c>
       <c r="R31" t="n">
-        <v>6952896.594094989</v>
+        <v>6949840</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4010,19 +3568,9 @@
           <t>2021-07-13</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4049,15 +3597,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>103381219</v>
+        <v>103381168</v>
       </c>
       <c r="B32" t="n">
-        <v>96336</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4065,21 +3608,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219811</v>
+        <v>219790</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4089,10 +3632,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>367915.8387967658</v>
+        <v>367443</v>
       </c>
       <c r="R32" t="n">
-        <v>6951007.437981394</v>
+        <v>6949785</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4122,19 +3665,9 @@
           <t>2021-07-13</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4161,15 +3694,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>103381208</v>
+        <v>103381169</v>
       </c>
       <c r="B33" t="n">
-        <v>96336</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4177,21 +3705,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219811</v>
+        <v>219790</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4201,10 +3729,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>367887.4439316164</v>
+        <v>367436</v>
       </c>
       <c r="R33" t="n">
-        <v>6951782.706029817</v>
+        <v>6949770</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4234,19 +3762,9 @@
           <t>2021-07-13</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4273,15 +3791,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>103381210</v>
+        <v>103381171</v>
       </c>
       <c r="B34" t="n">
-        <v>96336</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4289,21 +3802,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219811</v>
+        <v>219790</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4313,10 +3826,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>367914.5840490968</v>
+        <v>367453</v>
       </c>
       <c r="R34" t="n">
-        <v>6951517.156566191</v>
+        <v>6949770</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4346,19 +3859,9 @@
           <t>2021-07-13</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4385,15 +3888,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>103381154</v>
+        <v>103381172</v>
       </c>
       <c r="B35" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4401,21 +3899,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4425,10 +3923,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>367898.3916511303</v>
+        <v>367433</v>
       </c>
       <c r="R35" t="n">
-        <v>6950732.569733612</v>
+        <v>6949752</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4458,19 +3956,9 @@
           <t>2021-07-13</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4497,15 +3985,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>103381221</v>
+        <v>103381174</v>
       </c>
       <c r="B36" t="n">
-        <v>96356</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4513,21 +3996,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4537,10 +4020,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>367926.06777228</v>
+        <v>367393</v>
       </c>
       <c r="R36" t="n">
-        <v>6951009.788892222</v>
+        <v>6949463</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4570,19 +4053,9 @@
           <t>2021-07-13</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4609,15 +4082,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>103381218</v>
+        <v>103381176</v>
       </c>
       <c r="B37" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4649,10 +4117,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>367913.4823460932</v>
+        <v>367400</v>
       </c>
       <c r="R37" t="n">
-        <v>6951040.653881923</v>
+        <v>6949435</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4682,19 +4150,9 @@
           <t>2021-07-13</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4721,15 +4179,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>103381223</v>
+        <v>103381177</v>
       </c>
       <c r="B38" t="n">
-        <v>96336</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4737,21 +4190,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>219811</v>
+        <v>219790</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4761,10 +4214,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>367554.9633043763</v>
+        <v>367397</v>
       </c>
       <c r="R38" t="n">
-        <v>6952678.96130483</v>
+        <v>6949376</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4794,19 +4247,9 @@
           <t>2021-07-13</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4833,15 +4276,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>103381159</v>
+        <v>103381178</v>
       </c>
       <c r="B39" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4849,21 +4287,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4873,10 +4311,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>367892.5568888311</v>
+        <v>367395</v>
       </c>
       <c r="R39" t="n">
-        <v>6950782.489630096</v>
+        <v>6949367</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4906,19 +4344,9 @@
           <t>2021-07-13</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4945,15 +4373,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>103381261</v>
+        <v>103381179</v>
       </c>
       <c r="B40" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4985,10 +4408,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>366609.8489199351</v>
+        <v>367919</v>
       </c>
       <c r="R40" t="n">
-        <v>6954812.166492529</v>
+        <v>6951004</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5018,19 +4441,9 @@
           <t>2021-07-13</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5057,15 +4470,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>103381227</v>
+        <v>103381180</v>
       </c>
       <c r="B41" t="n">
-        <v>96336</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5073,21 +4481,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219811</v>
+        <v>219790</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5097,10 +4505,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>366959.4420067481</v>
+        <v>367382</v>
       </c>
       <c r="R41" t="n">
-        <v>6954101.80529454</v>
+        <v>6949365</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5130,19 +4538,9 @@
           <t>2021-07-13</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5169,15 +4567,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>103381140</v>
+        <v>103381183</v>
       </c>
       <c r="B42" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5185,21 +4578,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5209,10 +4602,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>367516.7263298405</v>
+        <v>367387</v>
       </c>
       <c r="R42" t="n">
-        <v>6949992.808706551</v>
+        <v>6949342</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5242,19 +4635,9 @@
           <t>2021-07-13</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5281,15 +4664,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>103381178</v>
+        <v>103381184</v>
       </c>
       <c r="B43" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5321,10 +4699,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>367394.821281023</v>
+        <v>367385</v>
       </c>
       <c r="R43" t="n">
-        <v>6949366.746667364</v>
+        <v>6949338</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5354,19 +4732,9 @@
           <t>2021-07-13</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5393,15 +4761,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>103381209</v>
+        <v>103381194</v>
       </c>
       <c r="B44" t="n">
-        <v>96336</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5409,21 +4772,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219811</v>
+        <v>219790</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5433,10 +4796,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>367654.1221535953</v>
+        <v>367736</v>
       </c>
       <c r="R44" t="n">
-        <v>6952499.334950152</v>
+        <v>6952323</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5466,19 +4829,9 @@
           <t>2021-07-13</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5505,15 +4858,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>103381207</v>
+        <v>103381202</v>
       </c>
       <c r="B45" t="n">
-        <v>96336</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5521,21 +4869,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219811</v>
+        <v>219790</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5545,10 +4893,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>367869.4726480977</v>
+        <v>367816</v>
       </c>
       <c r="R45" t="n">
-        <v>6951828.497116675</v>
+        <v>6951930</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5578,19 +4926,9 @@
           <t>2021-07-13</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5617,15 +4955,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>103381220</v>
+        <v>103381204</v>
       </c>
       <c r="B46" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5633,21 +4966,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5657,10 +4990,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>367558.1802830051</v>
+        <v>367683</v>
       </c>
       <c r="R46" t="n">
-        <v>6952667.337194932</v>
+        <v>6952489</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5690,19 +5023,9 @@
           <t>2021-07-13</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5729,15 +5052,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>103381243</v>
+        <v>103381205</v>
       </c>
       <c r="B47" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5769,10 +5087,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>367431.4212578268</v>
+        <v>367832</v>
       </c>
       <c r="R47" t="n">
-        <v>6952904.619226226</v>
+        <v>6951902</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5802,19 +5120,9 @@
           <t>2021-07-13</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5841,15 +5149,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>103381260</v>
+        <v>103381206</v>
       </c>
       <c r="B48" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5881,10 +5184,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>366622.3180990323</v>
+        <v>367848</v>
       </c>
       <c r="R48" t="n">
-        <v>6954790.52422967</v>
+        <v>6951885</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5914,19 +5217,9 @@
           <t>2021-07-13</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5953,15 +5246,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>103381236</v>
+        <v>103381215</v>
       </c>
       <c r="B49" t="n">
-        <v>96336</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5969,21 +5257,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219811</v>
+        <v>219790</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5993,10 +5281,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>367193.0107459489</v>
+        <v>367922</v>
       </c>
       <c r="R49" t="n">
-        <v>6953261.316601099</v>
+        <v>6951065</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6026,19 +5314,9 @@
           <t>2021-07-13</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6065,15 +5343,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>103381153</v>
+        <v>103381216</v>
       </c>
       <c r="B50" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6105,10 +5378,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>367897.7862607816</v>
+        <v>367921</v>
       </c>
       <c r="R50" t="n">
-        <v>6950694.408503374</v>
+        <v>6951057</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6138,19 +5411,9 @@
           <t>2021-07-13</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6177,15 +5440,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>103381150</v>
+        <v>103381218</v>
       </c>
       <c r="B51" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6217,10 +5475,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>367689.3886665977</v>
+        <v>367913</v>
       </c>
       <c r="R51" t="n">
-        <v>6950242.191255003</v>
+        <v>6951040</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6250,19 +5508,9 @@
           <t>2021-07-13</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6289,15 +5537,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>103381176</v>
+        <v>103381229</v>
       </c>
       <c r="B52" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6329,10 +5572,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>367399.8520472057</v>
+        <v>367096</v>
       </c>
       <c r="R52" t="n">
-        <v>6949434.662271122</v>
+        <v>6953752</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6362,19 +5605,9 @@
           <t>2021-07-13</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6401,15 +5634,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>103381181</v>
+        <v>103381234</v>
       </c>
       <c r="B53" t="n">
-        <v>96336</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6417,21 +5645,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>219811</v>
+        <v>219790</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6441,10 +5669,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>367914.8454087345</v>
+        <v>367168</v>
       </c>
       <c r="R53" t="n">
-        <v>6951005.637626459</v>
+        <v>6953351</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6474,19 +5702,9 @@
           <t>2021-07-13</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6513,15 +5731,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>103381193</v>
+        <v>103381239</v>
       </c>
       <c r="B54" t="n">
-        <v>95511</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6529,21 +5742,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221944</v>
+        <v>219790</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lopplummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6553,10 +5766,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>367723.3720154802</v>
+        <v>367234</v>
       </c>
       <c r="R54" t="n">
-        <v>6952354.470218086</v>
+        <v>6953226</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6586,19 +5799,9 @@
           <t>2021-07-13</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6625,15 +5828,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>103381202</v>
+        <v>103381243</v>
       </c>
       <c r="B55" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6665,10 +5863,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>367816.4265008466</v>
+        <v>367431</v>
       </c>
       <c r="R55" t="n">
-        <v>6951929.960814255</v>
+        <v>6952904</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6698,19 +5896,9 @@
           <t>2021-07-13</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6737,15 +5925,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>103381174</v>
+        <v>103381244</v>
       </c>
       <c r="B56" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6777,10 +5960,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>367393.5962226755</v>
+        <v>367436</v>
       </c>
       <c r="R56" t="n">
-        <v>6949462.528218168</v>
+        <v>6952896</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6810,19 +5993,9 @@
           <t>2021-07-13</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6849,15 +6022,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>103381144</v>
+        <v>103381246</v>
       </c>
       <c r="B57" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6865,21 +6033,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6889,10 +6057,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>367808.0784249112</v>
+        <v>367462</v>
       </c>
       <c r="R57" t="n">
-        <v>6950352.469164949</v>
+        <v>6952882</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6922,19 +6090,9 @@
           <t>2021-07-13</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6961,15 +6119,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>103381168</v>
+        <v>103381248</v>
       </c>
       <c r="B58" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7001,10 +6154,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>367443.4093116862</v>
+        <v>367471</v>
       </c>
       <c r="R58" t="n">
-        <v>6949784.985699547</v>
+        <v>6952825</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7034,19 +6187,9 @@
           <t>2021-07-13</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7073,15 +6216,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>103381206</v>
+        <v>102455274</v>
       </c>
       <c r="B59" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99120</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7089,37 +6227,47 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>219790</v>
+        <v>219811</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Bruksvallarna, Hjd</t>
+          <t>Lillåsen, Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>367847.7863871052</v>
+        <v>367602</v>
       </c>
       <c r="R59" t="n">
-        <v>6951885.01428475</v>
+        <v>6952660</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7143,29 +6291,19 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-21</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-21</t>
         </is>
       </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG59" t="b">
         <v>0</v>
@@ -7173,27 +6311,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Brita Danielsson</t>
+          <t>HELENE JOHANSSON</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Brita Danielsson, Anna Dahlin</t>
+          <t>HELENE JOHANSSON</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>103381163</v>
+        <v>103381145</v>
       </c>
       <c r="B60" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99120</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7201,21 +6334,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>219790</v>
+        <v>219811</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7225,10 +6358,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>367461.5807364698</v>
+        <v>367817</v>
       </c>
       <c r="R60" t="n">
-        <v>6949870.312718078</v>
+        <v>6950420</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7258,19 +6391,9 @@
           <t>2021-07-13</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7297,15 +6420,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>103381201</v>
+        <v>103381152</v>
       </c>
       <c r="B61" t="n">
-        <v>96336</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99120</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7337,10 +6455,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>367803.7356686802</v>
+        <v>367879</v>
       </c>
       <c r="R61" t="n">
-        <v>6951969.560286601</v>
+        <v>6950654</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7370,19 +6488,9 @@
           <t>2021-07-13</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2021-07-13</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7406,6 +6514,4191 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>103381162</v>
+      </c>
+      <c r="B62" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Bruksvallarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>367466</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6949897</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Brita Danielsson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Brita Danielsson, Anna Dahlin</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>103381181</v>
+      </c>
+      <c r="B63" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Bruksvallarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>367915</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6951005</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Brita Danielsson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Brita Danielsson, Anna Dahlin</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>103381195</v>
+      </c>
+      <c r="B64" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Bruksvallarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>367743</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6952320</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Brita Danielsson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Brita Danielsson, Anna Dahlin</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>103381197</v>
+      </c>
+      <c r="B65" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Bruksvallarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>367726</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6952113</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Brita Danielsson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Brita Danielsson, Anna Dahlin</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>103381198</v>
+      </c>
+      <c r="B66" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Bruksvallarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>367727</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6952097</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Brita Danielsson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Brita Danielsson, Anna Dahlin</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>103381199</v>
+      </c>
+      <c r="B67" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Bruksvallarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>367744</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6952037</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Brita Danielsson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Brita Danielsson, Anna Dahlin</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>103381200</v>
+      </c>
+      <c r="B68" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Bruksvallarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>367786</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6951978</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Brita Danielsson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Brita Danielsson, Anna Dahlin</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>103381201</v>
+      </c>
+      <c r="B69" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Bruksvallarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>367804</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6951970</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Brita Danielsson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Brita Danielsson, Anna Dahlin</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>103381207</v>
+      </c>
+      <c r="B70" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Bruksvallarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>367870</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6951828</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Brita Danielsson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Brita Danielsson, Anna Dahlin</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>103381208</v>
+      </c>
+      <c r="B71" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Bruksvallarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>367887</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6951783</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Brita Danielsson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Brita Danielsson, Anna Dahlin</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>103381209</v>
+      </c>
+      <c r="B72" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Bruksvallarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>367654</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6952500</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Brita Danielsson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Brita Danielsson, Anna Dahlin</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>103381210</v>
+      </c>
+      <c r="B73" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Bruksvallarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>367914</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6951517</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Brita Danielsson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Brita Danielsson, Anna Dahlin</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>103381212</v>
+      </c>
+      <c r="B74" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Bruksvallarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>367646</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6952550</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Brita Danielsson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Brita Danielsson, Anna Dahlin</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>103381219</v>
+      </c>
+      <c r="B75" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Bruksvallarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>367916</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6951007</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Brita Danielsson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Brita Danielsson, Anna Dahlin</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>103381223</v>
+      </c>
+      <c r="B76" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Bruksvallarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>367555</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6952679</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Brita Danielsson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Brita Danielsson, Anna Dahlin</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>103381236</v>
+      </c>
+      <c r="B77" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Bruksvallarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>367193</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6953261</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Brita Danielsson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Brita Danielsson, Anna Dahlin</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>103381160</v>
+      </c>
+      <c r="B78" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Bruksvallarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>367483</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6949909</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Brita Danielsson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Brita Danielsson, Anna Dahlin</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>103381182</v>
+      </c>
+      <c r="B79" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Bruksvallarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>367913</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6951004</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Brita Danielsson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Brita Danielsson, Anna Dahlin</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>103381221</v>
+      </c>
+      <c r="B80" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Bruksvallarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>367926</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6951010</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Brita Danielsson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Brita Danielsson, Anna Dahlin</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>95025210</v>
+      </c>
+      <c r="B81" t="n">
+        <v>99022</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Bastukroken, Härjedalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>367475</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6952798</v>
+      </c>
+      <c r="S81" t="n">
+        <v>25</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2021-07-22</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2021-07-22</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>103381193</v>
+      </c>
+      <c r="B82" t="n">
+        <v>97977</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Bruksvallarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>367723</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6952354</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Brita Danielsson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Brita Danielsson, Anna Dahlin</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>103381138</v>
+      </c>
+      <c r="B83" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Bruksvallarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>367503</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6949955</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Brita Danielsson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Brita Danielsson, Anna Dahlin</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>103381140</v>
+      </c>
+      <c r="B84" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Bruksvallarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>367517</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6949993</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Brita Danielsson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Brita Danielsson, Anna Dahlin</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>103381141</v>
+      </c>
+      <c r="B85" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Bruksvallarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>367524</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6950017</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Brita Danielsson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Brita Danielsson, Anna Dahlin</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>103381154</v>
+      </c>
+      <c r="B86" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Bruksvallarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>367898</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6950732</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Brita Danielsson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Brita Danielsson, Anna Dahlin</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>103381165</v>
+      </c>
+      <c r="B87" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Bruksvallarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>367471</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6949866</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Brita Danielsson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Brita Danielsson, Anna Dahlin</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>103381170</v>
+      </c>
+      <c r="B88" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Bruksvallarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>367932</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6950859</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Brita Danielsson</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Brita Danielsson, Anna Dahlin</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>103381214</v>
+      </c>
+      <c r="B89" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Bruksvallarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>367938</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6951367</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Brita Danielsson</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Brita Danielsson, Anna Dahlin</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>103381220</v>
+      </c>
+      <c r="B90" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Bruksvallarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>367558</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6952667</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Brita Danielsson</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Brita Danielsson, Anna Dahlin</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>103381224</v>
+      </c>
+      <c r="B91" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Bruksvallarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>367242</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6953225</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Brita Danielsson</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Brita Danielsson, Anna Dahlin</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>103381137</v>
+      </c>
+      <c r="B92" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Bruksvallarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>367475</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6949901</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Brita Danielsson</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Brita Danielsson, Anna Dahlin</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>103381139</v>
+      </c>
+      <c r="B93" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Bruksvallarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>367508</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6949958</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Brita Danielsson</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Brita Danielsson, Anna Dahlin</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>103381142</v>
+      </c>
+      <c r="B94" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Bruksvallarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>367524</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6950015</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Brita Danielsson</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Brita Danielsson, Anna Dahlin</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>103381143</v>
+      </c>
+      <c r="B95" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Bruksvallarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>367540</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6950038</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Brita Danielsson</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Brita Danielsson, Anna Dahlin</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>103381144</v>
+      </c>
+      <c r="B96" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Bruksvallarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>367808</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6950353</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Brita Danielsson</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Brita Danielsson, Anna Dahlin</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>103381158</v>
+      </c>
+      <c r="B97" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Bruksvallarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>367876</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6950783</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Brita Danielsson</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Brita Danielsson, Anna Dahlin</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>103381159</v>
+      </c>
+      <c r="B98" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Bruksvallarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>367893</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6950782</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Brita Danielsson</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Brita Danielsson, Anna Dahlin</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>103381213</v>
+      </c>
+      <c r="B99" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Bruksvallarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>367626</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6952596</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Brita Danielsson</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Brita Danielsson, Anna Dahlin</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>126197085</v>
+      </c>
+      <c r="B100" t="n">
+        <v>98050</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>222112</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Månlåsbräken</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Ingvallsvallen, Ramundberget., Hjd</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>367700</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6952275</v>
+      </c>
+      <c r="S100" t="n">
+        <v>25</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>I kanten av lägdan, vid en liten kulle.</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF100" t="inlineStr"/>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>103381156</v>
+      </c>
+      <c r="B101" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Bruksvallarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>367515</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6949983</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Brita Danielsson</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Brita Danielsson, Anna Dahlin</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>103381157</v>
+      </c>
+      <c r="B102" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Bruksvallarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>367883</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6950764</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Brita Danielsson</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Brita Danielsson, Anna Dahlin</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>95025454</v>
+      </c>
+      <c r="B103" t="n">
+        <v>95765</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>1004672</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Källmossor</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Philonotis</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Brid.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Bastukroken, Härjedalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>367483</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6952893</v>
+      </c>
+      <c r="S103" t="n">
+        <v>25</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2021-07-22</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2021-07-22</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>103381226</v>
+      </c>
+      <c r="B104" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Bruksvallarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>366987</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6954007</v>
+      </c>
+      <c r="S104" t="n">
+        <v>10</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Brita Danielsson</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Brita Danielsson, Anna Dahlin</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18885-2024 artfynd.xlsx
+++ b/artfynd/A 18885-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY104"/>
+  <dimension ref="A1:AZ104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381254</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381196</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -965,6 +980,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95024742</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95025201</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1163,6 +1188,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95025274</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1262,6 +1292,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95025423</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1363,6 +1398,11 @@
           <t>Adb inventering slåtterängar 2020-2021</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98105810</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1460,6 +1500,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381146</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1557,6 +1602,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381147</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1654,6 +1704,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381148</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1751,6 +1806,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381150</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1848,6 +1908,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381151</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1945,6 +2010,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381153</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2042,6 +2112,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381155</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2139,6 +2214,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381161</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2236,6 +2316,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381163</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2333,6 +2418,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381164</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2430,6 +2520,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381166</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2527,6 +2622,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381167</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2624,6 +2724,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381168</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2721,6 +2826,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381169</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2818,6 +2928,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381171</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2915,6 +3030,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381172</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3012,6 +3132,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381174</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3109,6 +3234,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381176</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3206,6 +3336,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381177</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3303,6 +3438,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381178</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3400,6 +3540,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381179</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3497,6 +3642,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381180</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3594,6 +3744,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381183</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3691,6 +3846,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381184</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3788,6 +3948,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381194</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3885,6 +4050,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381202</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3982,6 +4152,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381204</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4079,6 +4254,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381205</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4176,6 +4356,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381206</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4273,6 +4458,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381215</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4370,6 +4560,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381216</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4467,6 +4662,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381218</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4564,6 +4764,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381226</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4661,6 +4866,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381229</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4758,6 +4968,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381231</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4855,6 +5070,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381234</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4952,6 +5172,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381239</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5049,6 +5274,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381243</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5146,6 +5376,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381244</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5243,6 +5478,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381246</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5340,6 +5580,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381248</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5437,6 +5682,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381260</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5534,6 +5784,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381261</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5631,6 +5886,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381262</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5728,6 +5988,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381263</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5825,6 +6090,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381264</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5922,6 +6192,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381266</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6029,6 +6304,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102455274</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6126,6 +6406,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381145</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6223,6 +6508,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381152</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6320,6 +6610,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381162</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6417,6 +6712,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381181</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6514,6 +6814,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381195</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6611,6 +6916,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381197</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6708,6 +7018,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381198</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6805,6 +7120,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381199</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6902,6 +7222,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381200</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -6999,6 +7324,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381201</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7096,6 +7426,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381207</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7193,6 +7528,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381208</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7290,6 +7630,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381209</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7387,6 +7732,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381210</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7484,6 +7834,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381212</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7581,6 +7936,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381219</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7678,6 +8038,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381223</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7775,6 +8140,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381227</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7872,6 +8242,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381232</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -7969,6 +8344,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381236</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8066,6 +8446,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381249</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8163,6 +8548,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381160</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8260,6 +8650,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381182</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8357,6 +8752,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381221</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8456,6 +8856,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95025210</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8549,6 +8954,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381193</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8646,6 +9056,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381138</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8743,6 +9158,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381140</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8840,6 +9260,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381141</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -8937,6 +9362,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381154</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9034,6 +9464,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381165</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9131,6 +9566,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381170</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9228,6 +9668,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381214</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9325,6 +9770,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381220</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9422,6 +9872,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381224</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9519,6 +9974,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381137</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9616,6 +10076,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381139</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9713,6 +10178,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381142</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -9810,6 +10280,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381143</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -9907,6 +10382,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381144</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10004,6 +10484,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381158</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10101,6 +10586,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381159</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10198,6 +10688,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381213</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10295,6 +10790,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381241</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10406,6 +10906,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126197085</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10503,6 +11008,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381156</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10600,6 +11110,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103381157</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10699,8 +11214,118 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95025454</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>